--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17895" windowHeight="10170"/>
+    <workbookView windowWidth="12645" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,17 +32,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>##var#column</t>
   </si>
   <si>
+    <t>##type</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>程序中的字段名称</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -52,26 +58,47 @@
     <t>GameFps</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>帧数</t>
   </si>
   <si>
-    <t>##type</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>DefaultHeroId</t>
+  </si>
+  <si>
+    <t>默认英雄ID</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ChipsForPoints</t>
+  </si>
+  <si>
+    <t>多少筹码换1积分</t>
+  </si>
+  <si>
+    <t>ExchangePointsForGoldCoins</t>
+  </si>
+  <si>
+    <t>多少积分换1金币</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,22 +110,160 @@
       <sz val="12"/>
       <color rgb="FF24292E"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,12 +272,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -135,9 +486,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -158,17 +751,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -455,14 +1092,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="33.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
@@ -470,52 +1107,94 @@
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="1" ht="17.25" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4">
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="D4" s="4">
         <v>120</v>
       </c>
     </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>##var#column</t>
   </si>
@@ -86,6 +86,18 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>BasicBettingAmount</t>
+  </si>
+  <si>
+    <t>每关第1回合基础下注金额</t>
+  </si>
+  <si>
+    <t>AfterBettingAmount</t>
+  </si>
+  <si>
+    <t>后续每回合下注金额</t>
   </si>
 </sst>
 </file>
@@ -263,7 +275,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,12 +459,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,10 +733,10 @@
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1098,8 +1104,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="33.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
@@ -1192,6 +1198,34 @@
         <v>17</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView windowWidth="15690" windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>##var#column</t>
   </si>
@@ -98,6 +98,24 @@
   </si>
   <si>
     <t>后续每回合下注金额</t>
+  </si>
+  <si>
+    <t>ShopRefreshFirst</t>
+  </si>
+  <si>
+    <t>商店首次刷新费用</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>ShopRefreshAfter</t>
+  </si>
+  <si>
+    <t>商店后续刷新费用增长</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -1104,10 +1122,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="33.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="163.25" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
@@ -1226,6 +1245,34 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="20400" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1128,7 +1128,7 @@
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="163.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20400" windowHeight="14775"/>
+    <workbookView windowWidth="15015" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>##var#column</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>GoldIcon</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>金币道具icon</t>
+  </si>
+  <si>
+    <t>coin</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1273,6 +1285,20 @@
         <v>27</v>
       </c>
     </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15015" windowHeight="9060"/>
+    <workbookView windowWidth="14010" windowHeight="10905"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>##var#column</t>
   </si>
@@ -128,6 +128,12 @@
   </si>
   <si>
     <t>coin</t>
+  </si>
+  <si>
+    <t>TalentChestNeedGold</t>
+  </si>
+  <si>
+    <t>抽天赋所需金币</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1299,6 +1305,20 @@
         <v>31</v>
       </c>
     </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14010" windowHeight="10905"/>
+    <workbookView windowWidth="10875" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>##var#column</t>
   </si>
@@ -106,7 +106,7 @@
     <t>商店首次刷新费用</t>
   </si>
   <si>
-    <t>5</t>
+    <t>15</t>
   </si>
   <si>
     <t>ShopRefreshAfter</t>
@@ -115,6 +115,12 @@
     <t>商店后续刷新费用增长</t>
   </si>
   <si>
+    <t>ShopRefreshGoldUpNumMax</t>
+  </si>
+  <si>
+    <t>商店刷新费用增长次数上限</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -134,6 +140,15 @@
   </si>
   <si>
     <t>抽天赋所需金币</t>
+  </si>
+  <si>
+    <t>PlayerInitialGoldNum</t>
+  </si>
+  <si>
+    <t>每局初始金币数</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1288,35 +1303,63 @@
         <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10875" windowHeight="9750"/>
+    <workbookView windowWidth="12450" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>##var#column</t>
   </si>
@@ -148,7 +148,28 @@
     <t>每局初始金币数</t>
   </si>
   <si>
-    <t>120</t>
+    <t>140</t>
+  </si>
+  <si>
+    <t>DamageTurnToGold</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>局内伤害与金币的转换比例</t>
+  </si>
+  <si>
+    <t>12|1</t>
+  </si>
+  <si>
+    <t>KillMonsterGetGold</t>
+  </si>
+  <si>
+    <t>每击杀一名敌人给予结算金币加成</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1362,6 +1383,34 @@
         <v>38</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1439,23 +1439,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GuideEnabled</t>
+          <t>HeroReplyHpPerLevelClear</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>是否启用新手引导</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+          <t>每通过1关后,英雄回复最大生命值的百分比(0为不生效)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.625" customWidth="1" style="1" min="1" max="1"/>
@@ -1437,23 +1437,111 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>HeroReplyHpPerLevelClear</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>每通过1关后,英雄回复最大生命值的百分比(0为不生效)</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>EnergyMax</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>体力上限(每日回满到此值)</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>EnergyCostPerRun</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>每局消耗体力</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>EnergyDailyResetHour</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>每日体力重置时刻(凌晨X点跨日)</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>EnergyAdRefillDailyLimit</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>每日看广告补充体力次数</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
   <si>
     <t>##var#column</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>1.每次抽卡需要消耗金币|2.品质概率分布:普通-80%,稀有-40%,史诗-20%,传说-10%|3.每个天赋卡会有等级上限,重复抽取后可以提升等级</t>
+  </si>
+  <si>
+    <t>DefaultRelicNumMax</t>
+  </si>
+  <si>
+    <t>初始默认可携带圣物最大数量</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1546,6 +1552,20 @@
         <v>60</v>
       </c>
     </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="81">
   <si>
     <t>##var#column</t>
   </si>
@@ -220,6 +220,9 @@
     <t>初始默认可携带圣物最大数量</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>AdShopStaminaPerBuy</t>
   </si>
   <si>
@@ -266,6 +269,12 @@
   </si>
   <si>
     <t>传说品质圣物框颜色</t>
+  </si>
+  <si>
+    <t>DefaultSkillShuffleNum</t>
+  </si>
+  <si>
+    <t>每关默认搓牌使用次数</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1608,18 +1617,18 @@
         <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1627,13 +1636,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -1641,13 +1650,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1655,13 +1664,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1669,46 +1678,60 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17145" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t>##var#column</t>
   </si>
@@ -275,6 +275,18 @@
   </si>
   <si>
     <t>每关默认搓牌使用次数</t>
+  </si>
+  <si>
+    <t>DefaultSkillReplaceNum</t>
+  </si>
+  <si>
+    <t>每关默认换牌使用次数</t>
+  </si>
+  <si>
+    <t>DefaultSkillPerspectiveNum</t>
+  </si>
+  <si>
+    <t>每关默认看牌使用次数</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1734,6 +1746,34 @@
         <v>29</v>
       </c>
     </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
   <si>
     <t>##var#column</t>
   </si>
@@ -148,7 +148,7 @@
     <t>每局初始金币数</t>
   </si>
   <si>
-    <t>140</t>
+    <t>0</t>
   </si>
   <si>
     <t>DamageTurnToGold</t>
@@ -293,6 +293,15 @@
   </si>
   <si>
     <t>每次抽取天赋金币累加</t>
+  </si>
+  <si>
+    <t>EverySkillProvideGold</t>
+  </si>
+  <si>
+    <t>每有1个未使用的技能,结算时提供20金币</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1536,8 +1545,8 @@
       <c r="C17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="1">
-        <v>10</v>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1792,6 +1801,20 @@
       </c>
       <c r="D36" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16590" windowHeight="10440"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="91">
   <si>
     <t>##var#column</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>每次抽取天赋金币累加</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>EverySkillProvideGold</t>
@@ -1800,21 +1803,21 @@
         <v>86</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="16725" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,10 @@
     <t>TalentChestNeedGold</t>
   </si>
   <si>
-    <t>抽天赋所需金币</t>
+    <t>第一次抽取天赋所需金币</t>
+  </si>
+  <si>
+    <t>50</t>
   </si>
   <si>
     <t>PlayerInitialGoldNum</t>
@@ -293,9 +296,6 @@
   </si>
   <si>
     <t>每次抽取天赋金币累加</t>
-  </si>
-  <si>
-    <t>50</t>
   </si>
   <si>
     <t>EverySkillProvideGold</t>
@@ -1507,60 +1507,60 @@
         <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D18" s="6">
         <v>8</v>
@@ -1568,27 +1568,27 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>12</v>
@@ -1596,27 +1596,27 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>29</v>
@@ -1624,41 +1624,41 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -1666,13 +1666,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -1680,13 +1680,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -1694,13 +1694,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1708,57 +1708,57 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>29</v>
@@ -1766,13 +1766,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>12</v>
@@ -1780,13 +1780,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>12</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:4">

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16725" windowHeight="10200"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
     <t>天赋页面规则描述</t>
   </si>
   <si>
-    <t>1.每次抽卡需要消耗金币|2.品质概率分布:普通-80%,稀有-40%,史诗-20%|3.每个天赋卡会有等级上限,重复抽取后可以提升等级</t>
+    <t>1.每次抽卡需要消耗金币|2.品质概率分布:普通-80%,稀有-40%,终极-20%|3.每个天赋卡会有等级上限,重复抽取后可以提升等级</t>
   </si>
   <si>
     <t>DefaultRelicNumMax</t>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1370,10 +1370,8 @@
           <t>第一次抽取天赋所需金币</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D14" s="1" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -1861,22 +1859,22 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>PvpBotFillDelaySeconds</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>PVP排队多少秒未满4人时用机器人补满(0=立即补满)</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>10</v>
       </c>
     </row>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1083,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.625" customWidth="1" style="1" min="1" max="1"/>
@@ -1878,6 +1878,28 @@
         <v>10</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PvpHeroHpBoostPercent</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PVP英雄血量提升百分比(1300=提高1300%即14倍,0=不提升)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17190" windowHeight="11490"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -337,19 +337,19 @@
     <t>PVP圣物槽位解锁所需金币</t>
   </si>
   <si>
-    <t>40|60|80|120|150</t>
-  </si>
-  <si>
-    <t>PVPRelicNumMax</t>
-  </si>
-  <si>
-    <t>PVP玩家携带圣物数量上限</t>
+    <t>40|60|80|100|120|150</t>
+  </si>
+  <si>
+    <t>PVPRelicInitialRelicNum</t>
+  </si>
+  <si>
+    <t>PVP玩家初始携带圣物数量</t>
   </si>
   <si>
     <t>PVPOrdinaryRelicNum</t>
   </si>
   <si>
-    <t>PVP普通圣物数量</t>
+    <t>PVP普通圣物重复数量</t>
   </si>
   <si>
     <t>6</t>
@@ -358,19 +358,19 @@
     <t>PVPRareRelicNum</t>
   </si>
   <si>
-    <t>PVP稀有圣物数量</t>
+    <t>PVP稀有圣物重复数量</t>
   </si>
   <si>
     <t>PVPEpicRelicNum</t>
   </si>
   <si>
-    <t>PVP史诗圣物数量</t>
+    <t>PVP史诗圣物重复数量</t>
   </si>
   <si>
     <t>PVPLegendRelicNum</t>
   </si>
   <si>
-    <t>PVP传说圣物数量</t>
+    <t>PVP传说圣物重复数量</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1959,7 @@
         <v>103</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:4">

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="11880" windowHeight="12075"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="124">
   <si>
     <t>##var#column</t>
   </si>
@@ -371,6 +371,39 @@
   </si>
   <si>
     <t>PVP传说圣物重复数量</t>
+  </si>
+  <si>
+    <t>PVPRelicEffectMultiple</t>
+  </si>
+  <si>
+    <t>PVP圣物升级成长(3=翻三倍)</t>
+  </si>
+  <si>
+    <t>PVPWinningStreakGoldNum</t>
+  </si>
+  <si>
+    <t>PVP连胜/连败金币奖励(从5连胜/连败开始都是100)</t>
+  </si>
+  <si>
+    <t>20|40|60|80|100</t>
+  </si>
+  <si>
+    <t>PVPGoldInterestNum</t>
+  </si>
+  <si>
+    <t>PVP每拥有多少金币就额外提供多少利息</t>
+  </si>
+  <si>
+    <t>100|10</t>
+  </si>
+  <si>
+    <t>PVPGoldInterestNumMax</t>
+  </si>
+  <si>
+    <t>PVP拥有多少金币是利息达到峰值</t>
+  </si>
+  <si>
+    <t>500</t>
   </si>
 </sst>
 </file>
@@ -1383,12 +1416,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.25" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
@@ -2018,6 +2051,62 @@
         <v>56</v>
       </c>
     </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11880" windowHeight="12075"/>
+    <workbookView windowWidth="25080" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
   <si>
     <t>##var#column</t>
   </si>
@@ -325,12 +325,6 @@
     <t>1300</t>
   </si>
   <si>
-    <t>PvpRelicSynthesisNum</t>
-  </si>
-  <si>
-    <t>PVP圣物升级所需数量</t>
-  </si>
-  <si>
     <t>PVPRelicNumNeedGold</t>
   </si>
   <si>
@@ -352,9 +346,6 @@
     <t>PVP普通圣物重复数量</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>PVPRareRelicNum</t>
   </si>
   <si>
@@ -371,12 +362,6 @@
   </si>
   <si>
     <t>PVP传说圣物重复数量</t>
-  </si>
-  <si>
-    <t>PVPRelicEffectMultiple</t>
-  </si>
-  <si>
-    <t>PVP圣物升级成长(3=翻三倍)</t>
   </si>
   <si>
     <t>PVPWinningStreakGoldNum</t>
@@ -1416,7 +1401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="33.625" style="1" customWidth="1"/>
@@ -1954,31 +1939,31 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B41" t="s">
-        <v>8</v>
+      <c r="B41" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1992,7 +1977,7 @@
         <v>103</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2006,49 +1991,49 @@
         <v>105</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="D45" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2056,55 +2041,27 @@
         <v>113</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConst.xlsx
+++ b/Config/GameConst.xlsx
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>40|60|80|100|120|150</t>
+          <t>60|100|150|210|280|360</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>100|10</t>
+          <t>100|5</t>
         </is>
       </c>
     </row>
